--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G622"/>
+  <dimension ref="A1:G624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17176,6 +17176,60 @@
         <v>180.78</v>
       </c>
       <c r="G622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:56+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>157.38</v>
+      </c>
+      <c r="C623" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="D623" t="n">
+        <v>208.17</v>
+      </c>
+      <c r="E623" t="n">
+        <v>216.09</v>
+      </c>
+      <c r="F623" t="n">
+        <v>182.88</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="C624" t="n">
+        <v>166.13</v>
+      </c>
+      <c r="D624" t="n">
+        <v>209.84</v>
+      </c>
+      <c r="E624" t="n">
+        <v>217.86</v>
+      </c>
+      <c r="F624" t="n">
+        <v>188.02</v>
+      </c>
+      <c r="G624" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17192,7 +17246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B714"/>
+  <dimension ref="A1:B716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24335,6 +24389,26 @@
       </c>
       <c r="B714" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -24497,28 +24571,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1845126631146624</v>
+        <v>-0.2051105486842061</v>
       </c>
       <c r="J2" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K2" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00240322786076741</v>
+        <v>0.002974793179376878</v>
       </c>
       <c r="M2" t="n">
-        <v>19.93613074859718</v>
+        <v>20.03292679400028</v>
       </c>
       <c r="N2" t="n">
-        <v>816.440686887438</v>
+        <v>817.459598046702</v>
       </c>
       <c r="O2" t="n">
-        <v>28.57342623640781</v>
+        <v>28.59125037571288</v>
       </c>
       <c r="P2" t="n">
-        <v>196.3354053475538</v>
+        <v>196.5411070020065</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24569,28 +24643,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.532677997303644</v>
+        <v>-0.5575320853389322</v>
       </c>
       <c r="J3" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K3" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09024427742819041</v>
+        <v>0.09583062189815106</v>
       </c>
       <c r="M3" t="n">
-        <v>7.911743904161835</v>
+        <v>8.077251218255537</v>
       </c>
       <c r="N3" t="n">
-        <v>165.0042706682874</v>
+        <v>169.7696512858923</v>
       </c>
       <c r="O3" t="n">
-        <v>12.84539881312711</v>
+        <v>13.02956834610772</v>
       </c>
       <c r="P3" t="n">
-        <v>219.9087034141079</v>
+        <v>220.1578637049776</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24641,28 +24715,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3488044028696452</v>
+        <v>-0.3522466636606384</v>
       </c>
       <c r="J4" t="n">
+        <v>623</v>
+      </c>
+      <c r="K4" t="n">
         <v>621</v>
       </c>
-      <c r="K4" t="n">
-        <v>619</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1254282005571028</v>
+        <v>0.1281138751072284</v>
       </c>
       <c r="M4" t="n">
-        <v>5.667829960266755</v>
+        <v>5.668417916094922</v>
       </c>
       <c r="N4" t="n">
-        <v>48.82512991806657</v>
+        <v>48.77132800610816</v>
       </c>
       <c r="O4" t="n">
-        <v>6.987498115782684</v>
+        <v>6.983647185110955</v>
       </c>
       <c r="P4" t="n">
-        <v>223.7934867928797</v>
+        <v>223.82798484702</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24713,28 +24787,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4988110724110351</v>
+        <v>0.5005592582367449</v>
       </c>
       <c r="J5" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K5" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06842651020528134</v>
+        <v>0.06929793200620071</v>
       </c>
       <c r="M5" t="n">
-        <v>10.25600409386403</v>
+        <v>10.23279468879649</v>
       </c>
       <c r="N5" t="n">
-        <v>195.243228738686</v>
+        <v>194.6420218555049</v>
       </c>
       <c r="O5" t="n">
-        <v>13.97294631560166</v>
+        <v>13.951416482046</v>
       </c>
       <c r="P5" t="n">
-        <v>201.023379591079</v>
+        <v>201.0058649803518</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24785,28 +24859,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1987806483027219</v>
+        <v>-0.2011609831703653</v>
       </c>
       <c r="J6" t="n">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K6" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003396582099093992</v>
+        <v>0.003501228660764633</v>
       </c>
       <c r="M6" t="n">
-        <v>21.05004108341003</v>
+        <v>20.99300375397629</v>
       </c>
       <c r="N6" t="n">
-        <v>659.9100094453595</v>
+        <v>657.8017858756735</v>
       </c>
       <c r="O6" t="n">
-        <v>25.68871365883001</v>
+        <v>25.64764679021593</v>
       </c>
       <c r="P6" t="n">
-        <v>194.5000181163531</v>
+        <v>194.5242407821022</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24844,7 +24918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G622"/>
+  <dimension ref="A1:G624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47753,6 +47827,80 @@
         </is>
       </c>
     </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:07:56+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-43.63032173109053,172.68617648183343</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>-43.630901732849885,172.68677111254308</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>-43.631701753621854,172.68702548888157</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>-43.63228710952248,172.68761177179616</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>-43.632626100282415,172.68857874988282</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-43.630325025278125,172.68617139116938</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>-43.63091209263287,172.68675509756403</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>-43.631711754138536,172.68701002917157</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>-43.632297711017486,172.6875953888269</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>-43.63265688693944,172.68853117468757</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G624"/>
+  <dimension ref="A1:G626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17230,6 +17230,60 @@
         <v>188.02</v>
       </c>
       <c r="G624" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:54+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>160.13</v>
+      </c>
+      <c r="C625" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="D625" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="E625" t="n">
+        <v>218.45</v>
+      </c>
+      <c r="F625" t="n">
+        <v>189.63</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>178.05</v>
+      </c>
+      <c r="C626" t="n">
+        <v>191.91</v>
+      </c>
+      <c r="D626" t="n">
+        <v>214.42</v>
+      </c>
+      <c r="E626" t="n">
+        <v>220.68</v>
+      </c>
+      <c r="F626" t="n">
+        <v>196.55</v>
+      </c>
+      <c r="G626" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17246,7 +17300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B716"/>
+  <dimension ref="A1:B718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24409,6 +24463,26 @@
       </c>
       <c r="B716" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -24571,28 +24645,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2051105486842061</v>
+        <v>-0.2184561343045111</v>
       </c>
       <c r="J2" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K2" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002974793179376878</v>
+        <v>0.003388339958226627</v>
       </c>
       <c r="M2" t="n">
-        <v>20.03292679400028</v>
+        <v>20.07250442749545</v>
       </c>
       <c r="N2" t="n">
-        <v>817.459598046702</v>
+        <v>816.6417087305534</v>
       </c>
       <c r="O2" t="n">
-        <v>28.59125037571288</v>
+        <v>28.57694365621617</v>
       </c>
       <c r="P2" t="n">
-        <v>196.5411070020065</v>
+        <v>196.6746705241921</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24643,28 +24717,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5575320853389322</v>
+        <v>-0.5728066251519763</v>
       </c>
       <c r="J3" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K3" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09583062189815106</v>
+        <v>0.09992612907019927</v>
       </c>
       <c r="M3" t="n">
-        <v>8.077251218255537</v>
+        <v>8.170269051627638</v>
       </c>
       <c r="N3" t="n">
-        <v>169.7696512858923</v>
+        <v>171.6717304894694</v>
       </c>
       <c r="O3" t="n">
-        <v>13.02956834610772</v>
+        <v>13.10235591370763</v>
       </c>
       <c r="P3" t="n">
-        <v>220.1578637049776</v>
+        <v>220.3113144533386</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24715,28 +24789,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3522466636606384</v>
+        <v>-0.3534468869491718</v>
       </c>
       <c r="J4" t="n">
+        <v>625</v>
+      </c>
+      <c r="K4" t="n">
         <v>623</v>
       </c>
-      <c r="K4" t="n">
-        <v>621</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1281138751072284</v>
+        <v>0.1295780803608561</v>
       </c>
       <c r="M4" t="n">
-        <v>5.668417916094922</v>
+        <v>5.656748781715757</v>
       </c>
       <c r="N4" t="n">
-        <v>48.77132800610816</v>
+        <v>48.63805547700272</v>
       </c>
       <c r="O4" t="n">
-        <v>6.983647185110955</v>
+        <v>6.97409890071848</v>
       </c>
       <c r="P4" t="n">
-        <v>223.82798484702</v>
+        <v>223.840033933802</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24787,28 +24861,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5005592582367449</v>
+        <v>0.5038392189344101</v>
       </c>
       <c r="J5" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K5" t="n">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06929793200620071</v>
+        <v>0.07055193790972947</v>
       </c>
       <c r="M5" t="n">
-        <v>10.23279468879649</v>
+        <v>10.21840801216316</v>
       </c>
       <c r="N5" t="n">
-        <v>194.6420218555049</v>
+        <v>194.112662817832</v>
       </c>
       <c r="O5" t="n">
-        <v>13.951416482046</v>
+        <v>13.93243204963986</v>
       </c>
       <c r="P5" t="n">
-        <v>201.0058649803518</v>
+        <v>200.9729186442595</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24859,28 +24933,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2011609831703653</v>
+        <v>-0.198767066445853</v>
       </c>
       <c r="J6" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K6" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003501228660764633</v>
+        <v>0.003441203080242761</v>
       </c>
       <c r="M6" t="n">
-        <v>20.99300375397629</v>
+        <v>20.93671703940622</v>
       </c>
       <c r="N6" t="n">
-        <v>657.8017858756735</v>
+        <v>655.7259772983007</v>
       </c>
       <c r="O6" t="n">
-        <v>25.64764679021593</v>
+        <v>25.60714699645981</v>
       </c>
       <c r="P6" t="n">
-        <v>194.5242407821022</v>
+        <v>194.4997869121597</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24918,7 +24992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G624"/>
+  <dimension ref="A1:G626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47901,6 +47975,80 @@
         </is>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:54+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-43.63033820202624,172.68615102850757</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>-43.63092808142639,172.68673038079368</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>-43.631717203520985,172.68700160501604</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>-43.63230124484862,172.6875899278359</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>-43.63266653022672,172.68851627271957</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-43.63044553249172,172.6859851650401</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-43.63106647109409,172.68651644595312</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>-43.63173918069436,172.68696763065918</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>-43.632314601530034,172.68756928713518</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>-43.63270797837063,172.68845222197046</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G626"/>
+  <dimension ref="A1:G628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17284,6 +17284,60 @@
         <v>196.55</v>
       </c>
       <c r="G626" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>179.32</v>
+      </c>
+      <c r="C627" t="n">
+        <v>193.43</v>
+      </c>
+      <c r="D627" t="n">
+        <v>215.06</v>
+      </c>
+      <c r="E627" t="n">
+        <v>221.13</v>
+      </c>
+      <c r="F627" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:14:06+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>196.91</v>
+      </c>
+      <c r="C628" t="n">
+        <v>215.81</v>
+      </c>
+      <c r="D628" t="n">
+        <v>219.71</v>
+      </c>
+      <c r="E628" t="n">
+        <v>222.63</v>
+      </c>
+      <c r="F628" t="n">
+        <v>201.54</v>
+      </c>
+      <c r="G628" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17300,7 +17354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B718"/>
+  <dimension ref="A1:B720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24483,6 +24537,26 @@
       </c>
       <c r="B718" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -24645,28 +24719,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2184561343045111</v>
+        <v>-0.2201320282174357</v>
       </c>
       <c r="J2" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K2" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003388339958226627</v>
+        <v>0.003462166497408492</v>
       </c>
       <c r="M2" t="n">
-        <v>20.07250442749545</v>
+        <v>20.04070085926164</v>
       </c>
       <c r="N2" t="n">
-        <v>816.6417087305534</v>
+        <v>814.3085480988352</v>
       </c>
       <c r="O2" t="n">
-        <v>28.57694365621617</v>
+        <v>28.53609202569327</v>
       </c>
       <c r="P2" t="n">
-        <v>196.6746705241921</v>
+        <v>196.6914324855736</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24717,28 +24791,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5728066251519763</v>
+        <v>-0.5731553002609275</v>
       </c>
       <c r="J3" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K3" t="n">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09992612907019927</v>
+        <v>0.1004243231126175</v>
       </c>
       <c r="M3" t="n">
-        <v>8.170269051627638</v>
+        <v>8.180921250252418</v>
       </c>
       <c r="N3" t="n">
-        <v>171.6717304894694</v>
+        <v>171.524192227298</v>
       </c>
       <c r="O3" t="n">
-        <v>13.10235591370763</v>
+        <v>13.09672448466784</v>
       </c>
       <c r="P3" t="n">
-        <v>220.3113144533386</v>
+        <v>220.3147588039654</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24789,28 +24863,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3534468869491718</v>
+        <v>-0.3517181439764521</v>
       </c>
       <c r="J4" t="n">
+        <v>627</v>
+      </c>
+      <c r="K4" t="n">
         <v>625</v>
       </c>
-      <c r="K4" t="n">
-        <v>623</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1295780803608561</v>
+        <v>0.129126371960923</v>
       </c>
       <c r="M4" t="n">
-        <v>5.656748781715757</v>
+        <v>5.647433946683143</v>
       </c>
       <c r="N4" t="n">
-        <v>48.63805547700272</v>
+        <v>48.52563097878086</v>
       </c>
       <c r="O4" t="n">
-        <v>6.97409890071848</v>
+        <v>6.966034092565214</v>
       </c>
       <c r="P4" t="n">
-        <v>223.840033933802</v>
+        <v>223.822612898559</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24861,28 +24935,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5038392189344101</v>
+        <v>0.5084521847506601</v>
       </c>
       <c r="J5" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K5" t="n">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07055193790972947</v>
+        <v>0.07213848607632911</v>
       </c>
       <c r="M5" t="n">
-        <v>10.21840801216316</v>
+        <v>10.21182011389003</v>
       </c>
       <c r="N5" t="n">
-        <v>194.112662817832</v>
+        <v>193.6770348512017</v>
       </c>
       <c r="O5" t="n">
-        <v>13.93243204963986</v>
+        <v>13.91678967474905</v>
       </c>
       <c r="P5" t="n">
-        <v>200.9729186442595</v>
+        <v>200.926490569249</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24933,28 +25007,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.198767066445853</v>
+        <v>-0.192341921684273</v>
       </c>
       <c r="J6" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="K6" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003441203080242761</v>
+        <v>0.003242791861628458</v>
       </c>
       <c r="M6" t="n">
-        <v>20.93671703940622</v>
+        <v>20.90214415565994</v>
       </c>
       <c r="N6" t="n">
-        <v>655.7259772983007</v>
+        <v>653.9407132520053</v>
       </c>
       <c r="O6" t="n">
-        <v>25.60714699645981</v>
+        <v>25.57226453116746</v>
       </c>
       <c r="P6" t="n">
-        <v>194.4997869121597</v>
+        <v>194.4340626918688</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24992,7 +25066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G626"/>
+  <dimension ref="A1:G628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48049,6 +48123,80 @@
         </is>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:53+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-43.63045313905004,172.68597341018489</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-43.63107557329944,172.68650237491235</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>-43.63174301322492,172.68696170597312</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>-43.63231729682403,172.68756512197027</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>-43.6327157648676,172.68844018930545</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:14:06+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-43.63055849275107,172.68581060050792</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-43.6312095910929,172.68629519685996</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>-43.631770858945295,172.68691865940363</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>-43.63232628113623,172.6875512380845</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>-43.63273786653273,172.68840603503176</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G628"/>
+  <dimension ref="A1:G631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17338,6 +17338,87 @@
         <v>201.54</v>
       </c>
       <c r="G628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>207.05</v>
+      </c>
+      <c r="C629" t="n">
+        <v>213.85</v>
+      </c>
+      <c r="D629" t="n">
+        <v>217.79</v>
+      </c>
+      <c r="E629" t="n">
+        <v>220.31</v>
+      </c>
+      <c r="F629" t="n">
+        <v>206.86</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:38+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>207.05</v>
+      </c>
+      <c r="C630" t="n">
+        <v>213.84</v>
+      </c>
+      <c r="D630" t="n">
+        <v>217.96</v>
+      </c>
+      <c r="E630" t="n">
+        <v>220.37</v>
+      </c>
+      <c r="F630" t="n">
+        <v>206.92</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>207.22</v>
+      </c>
+      <c r="C631" t="n">
+        <v>212.4</v>
+      </c>
+      <c r="D631" t="n">
+        <v>216.43</v>
+      </c>
+      <c r="E631" t="n">
+        <v>218.71</v>
+      </c>
+      <c r="F631" t="n">
+        <v>205.73</v>
+      </c>
+      <c r="G631" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17354,7 +17435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B720"/>
+  <dimension ref="A1:B723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24557,6 +24638,36 @@
       </c>
       <c r="B720" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -24719,28 +24830,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2201320282174357</v>
+        <v>-0.2055364934533704</v>
       </c>
       <c r="J2" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="K2" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003462166497408492</v>
+        <v>0.003045396237923326</v>
       </c>
       <c r="M2" t="n">
-        <v>20.04070085926164</v>
+        <v>19.98610928177261</v>
       </c>
       <c r="N2" t="n">
-        <v>814.3085480988352</v>
+        <v>811.6684795606692</v>
       </c>
       <c r="O2" t="n">
-        <v>28.53609202569327</v>
+        <v>28.48979606035588</v>
       </c>
       <c r="P2" t="n">
-        <v>196.6914324855736</v>
+        <v>196.5442305809169</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24791,28 +24902,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5731553002609275</v>
+        <v>-0.5657410174066116</v>
       </c>
       <c r="J3" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="K3" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1004243231126175</v>
+        <v>0.09882056239855996</v>
       </c>
       <c r="M3" t="n">
-        <v>8.180921250252418</v>
+        <v>8.161949234941153</v>
       </c>
       <c r="N3" t="n">
-        <v>171.524192227298</v>
+        <v>171.0222954767778</v>
       </c>
       <c r="O3" t="n">
-        <v>13.09672448466784</v>
+        <v>13.0775492916975</v>
       </c>
       <c r="P3" t="n">
-        <v>220.3147588039654</v>
+        <v>220.2396960427176</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24863,28 +24974,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3517181439764521</v>
+        <v>-0.3491238003311689</v>
       </c>
       <c r="J4" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="K4" t="n">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="L4" t="n">
-        <v>0.129126371960923</v>
+        <v>0.1284986496812601</v>
       </c>
       <c r="M4" t="n">
-        <v>5.647433946683143</v>
+        <v>5.633469095447378</v>
       </c>
       <c r="N4" t="n">
-        <v>48.52563097878086</v>
+        <v>48.33496874679832</v>
       </c>
       <c r="O4" t="n">
-        <v>6.966034092565214</v>
+        <v>6.952335488654034</v>
       </c>
       <c r="P4" t="n">
-        <v>223.822612898559</v>
+        <v>223.7963581927875</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24935,28 +25046,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5084521847506601</v>
+        <v>0.5133373280036821</v>
       </c>
       <c r="J5" t="n">
+        <v>630</v>
+      </c>
+      <c r="K5" t="n">
         <v>627</v>
       </c>
-      <c r="K5" t="n">
-        <v>624</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.07213848607632911</v>
+        <v>0.07406621237416433</v>
       </c>
       <c r="M5" t="n">
-        <v>10.21182011389003</v>
+        <v>10.19042600941081</v>
       </c>
       <c r="N5" t="n">
-        <v>193.6770348512017</v>
+        <v>192.8914876576673</v>
       </c>
       <c r="O5" t="n">
-        <v>13.91678967474905</v>
+        <v>13.88853799568793</v>
       </c>
       <c r="P5" t="n">
-        <v>200.926490569249</v>
+        <v>200.8770763267094</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25007,28 +25118,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.192341921684273</v>
+        <v>-0.1765766997879295</v>
       </c>
       <c r="J6" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="K6" t="n">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003242791861628458</v>
+        <v>0.002755987423159079</v>
       </c>
       <c r="M6" t="n">
-        <v>20.90214415565994</v>
+        <v>20.88305637645028</v>
       </c>
       <c r="N6" t="n">
-        <v>653.9407132520053</v>
+        <v>652.1611420561173</v>
       </c>
       <c r="O6" t="n">
-        <v>25.57226453116746</v>
+        <v>25.53744587965127</v>
       </c>
       <c r="P6" t="n">
-        <v>194.4340626918688</v>
+        <v>194.2719822666515</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25066,7 +25177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G628"/>
+  <dimension ref="A1:G631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48197,6 +48308,117 @@
         </is>
       </c>
     </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-43.63061922524942,172.68571674634828</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-43.63119785407171,172.68631334117654</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>-43.63175936135952,172.68693643347586</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-43.632312385399295,172.68757271182608</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>-43.63276973124578,172.68835679359577</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:38+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-43.63061922524942,172.68571674634828</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-43.63119779418894,172.68631343374958</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>-43.631760379375045,172.68693485973014</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-43.63231274477185,172.68757215647082</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>-43.632770090622124,172.68835623824097</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-43.63062024344646,172.68571517285483</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-43.63118917106947,172.68632676426336</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>-43.63175121723456,172.68694902343958</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>-43.632302802130056,172.68758752129725</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-43.63276296299087,172.68836725277734</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G631"/>
+  <dimension ref="A1:G635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17419,6 +17419,114 @@
         <v>205.73</v>
       </c>
       <c r="G631" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:43+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>207.69</v>
+      </c>
+      <c r="C632" t="n">
+        <v>212.56</v>
+      </c>
+      <c r="D632" t="n">
+        <v>216.66</v>
+      </c>
+      <c r="E632" t="n">
+        <v>220.05</v>
+      </c>
+      <c r="F632" t="n">
+        <v>210.38</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>207.51</v>
+      </c>
+      <c r="C633" t="n">
+        <v>212.6</v>
+      </c>
+      <c r="D633" t="n">
+        <v>216.52</v>
+      </c>
+      <c r="E633" t="n">
+        <v>220.05</v>
+      </c>
+      <c r="F633" t="n">
+        <v>208.85</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:48+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>207.15</v>
+      </c>
+      <c r="C634" t="n">
+        <v>213.01</v>
+      </c>
+      <c r="D634" t="n">
+        <v>216.76</v>
+      </c>
+      <c r="E634" t="n">
+        <v>220.43</v>
+      </c>
+      <c r="F634" t="n">
+        <v>209.56</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="C635" t="n">
+        <v>213.07</v>
+      </c>
+      <c r="D635" t="n">
+        <v>216.83</v>
+      </c>
+      <c r="E635" t="n">
+        <v>220.63</v>
+      </c>
+      <c r="F635" t="n">
+        <v>208.64</v>
+      </c>
+      <c r="G635" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17435,7 +17543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B723"/>
+  <dimension ref="A1:B727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24668,6 +24776,46 @@
       </c>
       <c r="B723" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -24830,28 +24978,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2055364934533704</v>
+        <v>-0.186452087865404</v>
       </c>
       <c r="J2" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="K2" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003045396237923326</v>
+        <v>0.002535888939695585</v>
       </c>
       <c r="M2" t="n">
-        <v>19.98610928177261</v>
+        <v>19.91312689452414</v>
       </c>
       <c r="N2" t="n">
-        <v>811.6684795606692</v>
+        <v>808.1573346480484</v>
       </c>
       <c r="O2" t="n">
-        <v>28.48979606035588</v>
+        <v>28.42810817919561</v>
       </c>
       <c r="P2" t="n">
-        <v>196.5442305809169</v>
+        <v>196.3510218963241</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24902,28 +25050,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5657410174066116</v>
+        <v>-0.5567234560604366</v>
       </c>
       <c r="J3" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="K3" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09882056239855996</v>
+        <v>0.09696910883684995</v>
       </c>
       <c r="M3" t="n">
-        <v>8.161949234941153</v>
+        <v>8.135154629992277</v>
       </c>
       <c r="N3" t="n">
-        <v>171.0222954767778</v>
+        <v>170.2938873315873</v>
       </c>
       <c r="O3" t="n">
-        <v>13.0775492916975</v>
+        <v>13.04967000853229</v>
       </c>
       <c r="P3" t="n">
-        <v>220.2396960427176</v>
+        <v>220.1480404627141</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24974,28 +25122,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3491238003311689</v>
+        <v>-0.3465538829181993</v>
       </c>
       <c r="J4" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="K4" t="n">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1284986496812601</v>
+        <v>0.1282669641261935</v>
       </c>
       <c r="M4" t="n">
-        <v>5.633469095447378</v>
+        <v>5.610519437138537</v>
       </c>
       <c r="N4" t="n">
-        <v>48.33496874679832</v>
+        <v>48.05815650754204</v>
       </c>
       <c r="O4" t="n">
-        <v>6.952335488654034</v>
+        <v>6.932399044165161</v>
       </c>
       <c r="P4" t="n">
-        <v>223.7963581927875</v>
+        <v>223.7702453298595</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25046,28 +25194,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5133373280036821</v>
+        <v>0.5202136415245737</v>
       </c>
       <c r="J5" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="K5" t="n">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07406621237416433</v>
+        <v>0.07677362807687083</v>
       </c>
       <c r="M5" t="n">
-        <v>10.19042600941081</v>
+        <v>10.16421579267729</v>
       </c>
       <c r="N5" t="n">
-        <v>192.8914876576673</v>
+        <v>191.8772157757055</v>
       </c>
       <c r="O5" t="n">
-        <v>13.88853799568793</v>
+        <v>13.85197515792262</v>
       </c>
       <c r="P5" t="n">
-        <v>200.8770763267094</v>
+        <v>200.8072431808855</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25118,28 +25266,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1765766997879295</v>
+        <v>-0.1526498672746897</v>
       </c>
       <c r="J6" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="K6" t="n">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002755987423159079</v>
+        <v>0.002080742646626943</v>
       </c>
       <c r="M6" t="n">
-        <v>20.88305637645028</v>
+        <v>20.87381848439501</v>
       </c>
       <c r="N6" t="n">
-        <v>652.1611420561173</v>
+        <v>650.4209436707863</v>
       </c>
       <c r="O6" t="n">
-        <v>25.53744587965127</v>
+        <v>25.50335161642066</v>
       </c>
       <c r="P6" t="n">
-        <v>194.2719822666515</v>
+        <v>194.0250400234007</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25177,7 +25325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G631"/>
+  <dimension ref="A1:G635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48419,6 +48567,154 @@
         </is>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:43+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-43.63062305846169,172.68571082260797</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-43.63119012919393,172.68632528309536</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-43.63175259454991,172.6869468942548</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-43.63231082811817,172.68757511836546</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-43.63279081465309,172.68832421276747</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-43.63062198037077,172.68571248866</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-43.63119036872505,172.68632491280334</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>-43.63175175618405,172.68694819028033</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>-43.63231082811817,172.68757511836546</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>-43.6327816505596,172.68833837432348</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:48+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-43.63061982418886,172.6857158207639</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-43.63119282391887,172.6863211173101</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-43.63175319338266,172.68694596852222</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-43.632313104144416,172.68757160111556</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>-43.63278590317837,172.68833180262155</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-43.63061593108239,172.68572183706198</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-43.63119318321552,172.686320561872</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>-43.631753612565575,172.68694532050944</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-43.63231430205291,172.68756974993127</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>-43.63278039274271,172.68834031806614</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G635"/>
+  <dimension ref="A1:G637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17527,6 +17527,60 @@
         <v>208.64</v>
       </c>
       <c r="G635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>206.42</v>
+      </c>
+      <c r="C636" t="n">
+        <v>213.38</v>
+      </c>
+      <c r="D636" t="n">
+        <v>217.01</v>
+      </c>
+      <c r="E636" t="n">
+        <v>219.04</v>
+      </c>
+      <c r="F636" t="n">
+        <v>209.63</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>205.81</v>
+      </c>
+      <c r="C637" t="n">
+        <v>214.68</v>
+      </c>
+      <c r="D637" t="n">
+        <v>218.56</v>
+      </c>
+      <c r="E637" t="n">
+        <v>220.83</v>
+      </c>
+      <c r="F637" t="n">
+        <v>210.05</v>
+      </c>
+      <c r="G637" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17543,7 +17597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B727"/>
+  <dimension ref="A1:B729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24816,6 +24870,26 @@
       </c>
       <c r="B727" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -24978,28 +25052,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.186452087865404</v>
+        <v>-0.177740225187812</v>
       </c>
       <c r="J2" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K2" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002535888939695585</v>
+        <v>0.002318368549465655</v>
       </c>
       <c r="M2" t="n">
-        <v>19.91312689452414</v>
+        <v>19.87447082530699</v>
       </c>
       <c r="N2" t="n">
-        <v>808.1573346480484</v>
+        <v>806.291693467466</v>
       </c>
       <c r="O2" t="n">
-        <v>28.42810817919561</v>
+        <v>28.39527590053433</v>
       </c>
       <c r="P2" t="n">
-        <v>196.3510218963241</v>
+        <v>196.2623910260976</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25050,28 +25124,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5567234560604366</v>
+        <v>-0.551544700938953</v>
       </c>
       <c r="J3" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K3" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09696910883684995</v>
+        <v>0.09579620206690131</v>
       </c>
       <c r="M3" t="n">
-        <v>8.135154629992277</v>
+        <v>8.123822127021432</v>
       </c>
       <c r="N3" t="n">
-        <v>170.2938873315873</v>
+        <v>169.9939510317047</v>
       </c>
       <c r="O3" t="n">
-        <v>13.04967000853229</v>
+        <v>13.03817284099673</v>
       </c>
       <c r="P3" t="n">
-        <v>220.1480404627141</v>
+        <v>220.0951431204752</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25122,28 +25196,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3465538829181993</v>
+        <v>-0.3446250676445289</v>
       </c>
       <c r="J4" t="n">
+        <v>636</v>
+      </c>
+      <c r="K4" t="n">
         <v>634</v>
       </c>
-      <c r="K4" t="n">
-        <v>632</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1282669641261935</v>
+        <v>0.1276823381207205</v>
       </c>
       <c r="M4" t="n">
-        <v>5.610519437138537</v>
+        <v>5.602249544603017</v>
       </c>
       <c r="N4" t="n">
-        <v>48.05815650754204</v>
+        <v>47.94140212229173</v>
       </c>
       <c r="O4" t="n">
-        <v>6.932399044165161</v>
+        <v>6.923973001268256</v>
       </c>
       <c r="P4" t="n">
-        <v>223.7702453298595</v>
+        <v>223.7505490500682</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25194,28 +25268,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5202136415245737</v>
+        <v>0.5233399718181806</v>
       </c>
       <c r="J5" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K5" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07677362807687083</v>
+        <v>0.07807106108548512</v>
       </c>
       <c r="M5" t="n">
-        <v>10.16421579267729</v>
+        <v>10.14941512348147</v>
       </c>
       <c r="N5" t="n">
-        <v>191.8772157757055</v>
+        <v>191.3601316696495</v>
       </c>
       <c r="O5" t="n">
-        <v>13.85197515792262</v>
+        <v>13.83329793178942</v>
       </c>
       <c r="P5" t="n">
-        <v>200.8072431808855</v>
+        <v>200.7753358911585</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25266,28 +25340,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1526498672746897</v>
+        <v>-0.1406231095465203</v>
       </c>
       <c r="J6" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K6" t="n">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002080742646626943</v>
+        <v>0.001774664781840407</v>
       </c>
       <c r="M6" t="n">
-        <v>20.87381848439501</v>
+        <v>20.86899183256191</v>
       </c>
       <c r="N6" t="n">
-        <v>650.4209436707863</v>
+        <v>649.5843631972277</v>
       </c>
       <c r="O6" t="n">
-        <v>25.50335161642066</v>
+        <v>25.48694495613838</v>
       </c>
       <c r="P6" t="n">
-        <v>194.0250400234007</v>
+        <v>193.9003010008172</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25325,7 +25399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G635"/>
+  <dimension ref="A1:G637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48715,6 +48789,80 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-43.6306154519308,172.68572257752936</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-43.631195039581506,172.68631769210856</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-43.631754690464504,172.68694365419074</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-43.6323047786795,172.6875844668442</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>-43.63278632245063,172.68833115470724</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-43.63061179839978,172.68572822359292</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-43.63120282434125,172.68630565761475</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-43.63176397237081,172.68692930533314</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-43.63231549996138,172.68756789874695</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>-43.63278883808407,172.6883272672211</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G637"/>
+  <dimension ref="A1:G640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17581,6 +17581,87 @@
         <v>210.05</v>
       </c>
       <c r="G637" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:30+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>204.7</v>
+      </c>
+      <c r="C638" t="n">
+        <v>211.48</v>
+      </c>
+      <c r="D638" t="n">
+        <v>217.03</v>
+      </c>
+      <c r="E638" t="n">
+        <v>220.07</v>
+      </c>
+      <c r="F638" t="n">
+        <v>209.07</v>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>205.21</v>
+      </c>
+      <c r="C639" t="n">
+        <v>211.63</v>
+      </c>
+      <c r="D639" t="n">
+        <v>217.16</v>
+      </c>
+      <c r="E639" t="n">
+        <v>220.21</v>
+      </c>
+      <c r="F639" t="n">
+        <v>206.06</v>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:56+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>205.14</v>
+      </c>
+      <c r="C640" t="n">
+        <v>210.96</v>
+      </c>
+      <c r="D640" t="n">
+        <v>216.85</v>
+      </c>
+      <c r="E640" t="n">
+        <v>219.93</v>
+      </c>
+      <c r="F640" t="n">
+        <v>203.64</v>
+      </c>
+      <c r="G640" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17597,7 +17678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B729"/>
+  <dimension ref="A1:B732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24890,6 +24971,36 @@
       </c>
       <c r="B729" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -25052,28 +25163,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.177740225187812</v>
+        <v>-0.1658671556752184</v>
       </c>
       <c r="J2" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K2" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002318368549465655</v>
+        <v>0.002037527142889184</v>
       </c>
       <c r="M2" t="n">
-        <v>19.87447082530699</v>
+        <v>19.81360146047631</v>
       </c>
       <c r="N2" t="n">
-        <v>806.291693467466</v>
+        <v>803.349985481615</v>
       </c>
       <c r="O2" t="n">
-        <v>28.39527590053433</v>
+        <v>28.34342931759696</v>
       </c>
       <c r="P2" t="n">
-        <v>196.2623910260976</v>
+        <v>196.1412442813771</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25124,28 +25235,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.551544700938953</v>
+        <v>-0.546253670146417</v>
       </c>
       <c r="J3" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K3" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09579620206690131</v>
+        <v>0.09490211469611953</v>
       </c>
       <c r="M3" t="n">
-        <v>8.123822127021432</v>
+        <v>8.100150373480416</v>
       </c>
       <c r="N3" t="n">
-        <v>169.9939510317047</v>
+        <v>169.3573293314943</v>
       </c>
       <c r="O3" t="n">
-        <v>13.03817284099673</v>
+        <v>13.01373617880332</v>
       </c>
       <c r="P3" t="n">
-        <v>220.0951431204752</v>
+        <v>220.0409459421698</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25196,28 +25307,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3446250676445289</v>
+        <v>-0.3424474718356151</v>
       </c>
       <c r="J4" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K4" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1276823381207205</v>
+        <v>0.127310411277643</v>
       </c>
       <c r="M4" t="n">
-        <v>5.602249544603017</v>
+        <v>5.586472639440426</v>
       </c>
       <c r="N4" t="n">
-        <v>47.94140212229173</v>
+        <v>47.74391774316224</v>
       </c>
       <c r="O4" t="n">
-        <v>6.923973001268256</v>
+        <v>6.909697369868107</v>
       </c>
       <c r="P4" t="n">
-        <v>223.7505490500682</v>
+        <v>223.7282517075733</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25268,28 +25379,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5233399718181806</v>
+        <v>0.5280327162916842</v>
       </c>
       <c r="J5" t="n">
+        <v>639</v>
+      </c>
+      <c r="K5" t="n">
         <v>636</v>
       </c>
-      <c r="K5" t="n">
-        <v>633</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.07807106108548512</v>
+        <v>0.08004297332055832</v>
       </c>
       <c r="M5" t="n">
-        <v>10.14941512348147</v>
+        <v>10.12740869823338</v>
       </c>
       <c r="N5" t="n">
-        <v>191.3601316696495</v>
+        <v>190.5889354597486</v>
       </c>
       <c r="O5" t="n">
-        <v>13.83329793178942</v>
+        <v>13.80539515768196</v>
       </c>
       <c r="P5" t="n">
-        <v>200.7753358911585</v>
+        <v>200.7273079603314</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25340,28 +25451,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1406231095465203</v>
+        <v>-0.1261431415554663</v>
       </c>
       <c r="J6" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K6" t="n">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001774664781840407</v>
+        <v>0.001439947703930411</v>
       </c>
       <c r="M6" t="n">
-        <v>20.86899183256191</v>
+        <v>20.84301325605735</v>
       </c>
       <c r="N6" t="n">
-        <v>649.5843631972277</v>
+        <v>647.7085621506571</v>
       </c>
       <c r="O6" t="n">
-        <v>25.48694495613838</v>
+        <v>25.45011909894838</v>
       </c>
       <c r="P6" t="n">
-        <v>193.9003010008172</v>
+        <v>193.7497059364813</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25399,7 +25510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G637"/>
+  <dimension ref="A1:G640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48863,6 +48974,117 @@
         </is>
       </c>
     </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:30+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-43.63060515017049,172.68573849757567</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-43.63118366185341,172.68633528097854</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-43.63175481023104,172.68694346904422</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-43.63231094790904,172.68757493324705</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-43.63278296827251,172.68833633802157</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-43.630608204762446,172.6857337770974</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-43.63118456009521,172.68633389238377</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-43.631755588713574,172.68694226559182</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-43.63231178644503,172.68757363741815</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-43.63276493956099,172.68836419832633</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:06:56+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-43.63060778550472,172.6857344250062</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-43.63118054794841,172.68634009477336</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-43.631753732332115,172.68694513536292</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-43.63231010937303,172.68757622907592</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-43.6327504447115,172.68838659762903</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0581/nzd0581.xlsx
+++ b/data/nzd0581/nzd0581.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G640"/>
+  <dimension ref="A1:G642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17662,6 +17662,60 @@
         <v>203.64</v>
       </c>
       <c r="G640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>191.21</v>
+      </c>
+      <c r="C641" t="n">
+        <v>195.4</v>
+      </c>
+      <c r="D641" t="n">
+        <v>210.67</v>
+      </c>
+      <c r="E641" t="n">
+        <v>218.77</v>
+      </c>
+      <c r="F641" t="n">
+        <v>199.89</v>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>179.01</v>
+      </c>
+      <c r="C642" t="n">
+        <v>181.64</v>
+      </c>
+      <c r="D642" t="n">
+        <v>208.02</v>
+      </c>
+      <c r="E642" t="n">
+        <v>218.77</v>
+      </c>
+      <c r="F642" t="n">
+        <v>196.64</v>
+      </c>
+      <c r="G642" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17678,7 +17732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B732"/>
+  <dimension ref="A1:B734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25001,6 +25055,26 @@
       </c>
       <c r="B732" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -25163,28 +25237,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1658671556752184</v>
+        <v>-0.1697254237666881</v>
       </c>
       <c r="J2" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K2" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002037527142889184</v>
+        <v>0.002146664165753376</v>
       </c>
       <c r="M2" t="n">
-        <v>19.81360146047631</v>
+        <v>19.78203849782074</v>
       </c>
       <c r="N2" t="n">
-        <v>803.349985481615</v>
+        <v>801.0934558117933</v>
       </c>
       <c r="O2" t="n">
-        <v>28.34342931759696</v>
+        <v>28.30359439738694</v>
       </c>
       <c r="P2" t="n">
-        <v>196.1412442813771</v>
+        <v>196.1807938605526</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25235,28 +25309,28 @@
         <v>0.0453</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.546253670146417</v>
+        <v>-0.5561808404409335</v>
       </c>
       <c r="J3" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K3" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09490211469611953</v>
+        <v>0.09808453576570819</v>
       </c>
       <c r="M3" t="n">
-        <v>8.100150373480416</v>
+        <v>8.15273387896681</v>
       </c>
       <c r="N3" t="n">
-        <v>169.3573293314943</v>
+        <v>169.8607879313796</v>
       </c>
       <c r="O3" t="n">
-        <v>13.01373617880332</v>
+        <v>13.03306517789962</v>
       </c>
       <c r="P3" t="n">
-        <v>220.0409459421698</v>
+        <v>220.1430871227019</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25307,28 +25381,28 @@
         <v>0.0335</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3424474718356151</v>
+        <v>-0.345506975903624</v>
       </c>
       <c r="J4" t="n">
+        <v>641</v>
+      </c>
+      <c r="K4" t="n">
         <v>639</v>
       </c>
-      <c r="K4" t="n">
-        <v>637</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.127310411277643</v>
+        <v>0.1298346294905227</v>
       </c>
       <c r="M4" t="n">
-        <v>5.586472639440426</v>
+        <v>5.586549482518355</v>
       </c>
       <c r="N4" t="n">
-        <v>47.74391774316224</v>
+        <v>47.68394908328538</v>
       </c>
       <c r="O4" t="n">
-        <v>6.909697369868107</v>
+        <v>6.905356550047606</v>
       </c>
       <c r="P4" t="n">
-        <v>223.7282517075733</v>
+        <v>223.759716147806</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25379,28 +25453,28 @@
         <v>0.033</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5280327162916842</v>
+        <v>0.5303197996046429</v>
       </c>
       <c r="J5" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K5" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08004297332055832</v>
+        <v>0.081155347164661</v>
       </c>
       <c r="M5" t="n">
-        <v>10.12740869823338</v>
+        <v>10.10815730544023</v>
       </c>
       <c r="N5" t="n">
-        <v>190.5889354597486</v>
+        <v>190.0385149475887</v>
       </c>
       <c r="O5" t="n">
-        <v>13.80539515768196</v>
+        <v>13.78544576528408</v>
       </c>
       <c r="P5" t="n">
-        <v>200.7273079603314</v>
+        <v>200.7038013892918</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25451,28 +25525,28 @@
         <v>0.028</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1261431415554663</v>
+        <v>-0.1214197228209297</v>
       </c>
       <c r="J6" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K6" t="n">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001439947703930411</v>
+        <v>0.001342698700730893</v>
       </c>
       <c r="M6" t="n">
-        <v>20.84301325605735</v>
+        <v>20.8004259895385</v>
       </c>
       <c r="N6" t="n">
-        <v>647.7085621506571</v>
+        <v>645.8387750646839</v>
       </c>
       <c r="O6" t="n">
-        <v>25.45011909894838</v>
+        <v>25.41335820124298</v>
       </c>
       <c r="P6" t="n">
-        <v>193.7497059364813</v>
+        <v>193.7003684524775</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25510,7 +25584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G640"/>
+  <dimension ref="A1:G642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49085,6 +49159,80 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-43.63052435314663,172.68586335868042</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-43.63108737023402,172.6864841380966</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-43.63171672445442,172.6870023456012</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-43.63230316150269,172.6875869659422</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-43.63272798367562,172.68842130727106</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-43.63045128233119,172.68597627948054</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-43.63100497127899,172.6866115179398</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-43.631700855371754,172.68702687747802</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-43.63230316150269,172.6875869659422</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-43.63270851743585,172.6884513889399</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
